--- a/reports/溫室庫存月報表_2026_08.xlsx
+++ b/reports/溫室庫存月報表_2026_08.xlsx
@@ -8,9 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="庫存匯總表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="一號溫室" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="二號溫室" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="三號溫室" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="研究中心" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="埤子頭" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="四湖" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +531,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>一號溫室</t>
+          <t>研究中心</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>二號溫室</t>
+          <t>埤子頭</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">

--- a/reports/溫室庫存月報表_2026_08.xlsx
+++ b/reports/溫室庫存月報表_2026_08.xlsx
@@ -499,17 +499,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>品項編碼</t>
+          <t>單位</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>期初庫存</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>期初庫存</t>
+          <t>本月進庫</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -541,16 +541,14 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>FERT-001</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
           <t>公斤</t>
         </is>
       </c>
+      <c r="D2" s="4" t="n">
+        <v>80</v>
+      </c>
       <c r="E2" s="4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F2" s="4" t="n">
         <v>50</v>
@@ -575,16 +573,14 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>SEED-002</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
           <t>公克</t>
         </is>
       </c>
+      <c r="D3" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" s="7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" s="7" t="n">
         <v>10</v>
@@ -627,17 +623,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>品項編碼</t>
+          <t>單位</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>期初庫存</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>期初庫存</t>
+          <t>本月進庫</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -664,16 +660,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>FERT-001</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
           <t>公斤</t>
         </is>
       </c>
+      <c r="C2" s="4" t="n">
+        <v>80</v>
+      </c>
       <c r="D2" s="4" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>50</v>
@@ -716,17 +710,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>品項編碼</t>
+          <t>單位</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>期初庫存</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>期初庫存</t>
+          <t>本月進庫</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -753,16 +747,14 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>SEED-002</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
           <t>公克</t>
         </is>
       </c>
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="D2" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>10</v>
@@ -785,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -794,7 +786,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -805,30 +796,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>品項編碼</t>
+          <t>單位</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>單位</t>
+          <t>期初庫存</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>期初庫存</t>
+          <t>本月進庫</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>本月進庫</t>
+          <t>本月出庫</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>本月出庫</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>期末庫存</t>
         </is>
